--- a/trading-view/pine_scripts/01-supertrend/strategy_rankings.xlsx
+++ b/trading-view/pine_scripts/01-supertrend/strategy_rankings.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,41 +497,41 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>supertrend_v3_strict</t>
+          <t>supertrend_v7a_rsi_entry</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>423</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>-8.065</v>
+        <v>4.8475</v>
       </c>
       <c r="E2" t="n">
-        <v>-14.985</v>
+        <v>-2.9225</v>
       </c>
       <c r="F2" t="n">
-        <v>41.9425</v>
+        <v>59.91</v>
       </c>
       <c r="G2" t="n">
-        <v>0.78255</v>
+        <v>2.45795</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.48445</v>
+        <v>0.325175</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.169625</v>
+        <v>0.4405250000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1.6225</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>14.7525</v>
       </c>
       <c r="L2" t="n">
-        <v>72.95</v>
+        <v>98.0775</v>
       </c>
       <c r="M2" t="n">
-        <v>24.3175</v>
+        <v>38.15</v>
       </c>
       <c r="N2" t="n">
         <v>4</v>
@@ -543,41 +543,41 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>supertrend_v5_conservative</t>
+          <t>supertrend_v7d_half_equity</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1086</v>
+        <v>96</v>
       </c>
       <c r="D3" t="n">
-        <v>-15.1425</v>
+        <v>1.1725</v>
       </c>
       <c r="E3" t="n">
-        <v>-18.75</v>
+        <v>-3.005</v>
       </c>
       <c r="F3" t="n">
-        <v>31.62</v>
+        <v>52.425</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7318750000000001</v>
+        <v>1.330875</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0208</v>
+        <v>-0.001549999999999982</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.270275</v>
+        <v>0.20855</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>9.782500000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>65.10250000000001</v>
+        <v>97.765</v>
       </c>
       <c r="M3" t="n">
-        <v>21.6975</v>
+        <v>36.0925</v>
       </c>
       <c r="N3" t="n">
         <v>4</v>
@@ -589,41 +589,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>supertrend_v4_trend</t>
+          <t>supertrend_v6b_ultra</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1185</v>
+        <v>96</v>
       </c>
       <c r="D4" t="n">
-        <v>-19.67</v>
+        <v>2.225</v>
       </c>
       <c r="E4" t="n">
-        <v>-38.8675</v>
+        <v>-5.949999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>32.3325</v>
+        <v>52.425</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8815</v>
+        <v>1.3142</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2703</v>
+        <v>-0.001549999999999982</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.176025</v>
+        <v>0.202125</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>9.6275</v>
       </c>
       <c r="L4" t="n">
-        <v>24.0725</v>
+        <v>91.77</v>
       </c>
       <c r="M4" t="n">
-        <v>8.022500000000001</v>
+        <v>34.275</v>
       </c>
       <c r="N4" t="n">
         <v>4</v>
@@ -635,41 +635,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>supertrend_v1</t>
+          <t>supertrend_v7b_no_stop</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16210</v>
+        <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>-98.8725</v>
+        <v>2.8725</v>
       </c>
       <c r="E5" t="n">
-        <v>-98.905</v>
+        <v>-7.6425</v>
       </c>
       <c r="F5" t="n">
-        <v>21.3225</v>
+        <v>60.14</v>
       </c>
       <c r="G5" t="n">
-        <v>0.681625</v>
+        <v>1.25385</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.352275000000001</v>
+        <v>0.145</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.333225</v>
+        <v>0.148175</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5.967499999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>88.24250000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>31.815</v>
       </c>
       <c r="N5" t="n">
         <v>4</v>
@@ -681,43 +681,273 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>supertrend_v7c_hard_only</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>96</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.8725</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-7.6425</v>
+      </c>
+      <c r="F6" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.25385</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.148175</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.967499999999999</v>
+      </c>
+      <c r="L6" t="n">
+        <v>88.24250000000001</v>
+      </c>
+      <c r="M6" t="n">
+        <v>31.815</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>supertrend_v3_strict</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>423</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-8.065</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-14.985</v>
+      </c>
+      <c r="F7" t="n">
+        <v>41.9425</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.78255</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.48445</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.169625</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>72.95</v>
+      </c>
+      <c r="M7" t="n">
+        <v>24.3175</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>supertrend_v5_conservative</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1086</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-15.1425</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-18.75</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7318750000000001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-1.0208</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.270275</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>65.10250000000001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>21.6975</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>supertrend_v4_trend</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1185</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-19.67</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-38.8675</v>
+      </c>
+      <c r="F9" t="n">
+        <v>32.3325</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8815</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.2703</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.176025</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>24.0725</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8.022500000000001</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>supertrend_v2</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C10" t="n">
         <v>4793</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D10" t="n">
         <v>-79.31</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E10" t="n">
         <v>-80.4175</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F10" t="n">
         <v>27.055</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G10" t="n">
         <v>0.61105</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H10" t="n">
         <v>-3.635575</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I10" t="n">
         <v>-0.32855</v>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>supertrend_v1</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>16210</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-98.8725</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-98.905</v>
+      </c>
+      <c r="F11" t="n">
+        <v>21.3225</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.681625</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-4.352275000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.333225</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -732,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH61"/>
+  <dimension ref="A1:AH121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7622,6 +7852,6726 @@
         <v>28.01</v>
       </c>
       <c r="AH61" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>supertrend_v6b_ultra</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>27</v>
+      </c>
+      <c r="D62" t="n">
+        <v>13</v>
+      </c>
+      <c r="E62" t="n">
+        <v>14</v>
+      </c>
+      <c r="F62" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="G62" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="H62" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="I62" t="n">
+        <v>115.36</v>
+      </c>
+      <c r="J62" t="n">
+        <v>-59.57</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1.9367</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-34.81</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-3.44</v>
+      </c>
+      <c r="N62" t="n">
+        <v>2.0665</v>
+      </c>
+      <c r="O62" t="n">
+        <v>8.873900000000001</v>
+      </c>
+      <c r="P62" t="n">
+        <v>-4.2547</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>2.0857</v>
+      </c>
+      <c r="R62" t="n">
+        <v>2.0665</v>
+      </c>
+      <c r="S62" t="n">
+        <v>3</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0.5794</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0.5412</v>
+      </c>
+      <c r="W62" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="X62" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1055.8</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>BTCUSD</t>
+        </is>
+      </c>
+      <c r="AD62" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>18.04</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>97</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>38.97</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>supertrend_v6b_ultra</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>21</v>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="n">
+        <v>11</v>
+      </c>
+      <c r="F63" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="G63" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I63" t="n">
+        <v>72.22</v>
+      </c>
+      <c r="J63" t="n">
+        <v>-54.79</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-34.81</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-3.44</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.8296</v>
+      </c>
+      <c r="O63" t="n">
+        <v>7.2217</v>
+      </c>
+      <c r="P63" t="n">
+        <v>-4.9813</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1.4497</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0.8296</v>
+      </c>
+      <c r="S63" t="n">
+        <v>3</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0.2415</v>
+      </c>
+      <c r="W63" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="X63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1017.42</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>BTCUSD</t>
+        </is>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>97</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>supertrend_v6b_ultra</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>6</v>
+      </c>
+      <c r="D64" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" t="n">
+        <v>50</v>
+      </c>
+      <c r="G64" t="n">
+        <v>37.72</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I64" t="n">
+        <v>42.41</v>
+      </c>
+      <c r="J64" t="n">
+        <v>-4.69</v>
+      </c>
+      <c r="K64" t="n">
+        <v>9.0436</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="N64" t="n">
+        <v>6.2861</v>
+      </c>
+      <c r="O64" t="n">
+        <v>14.1352</v>
+      </c>
+      <c r="P64" t="n">
+        <v>-1.563</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>9.0436</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6.2861</v>
+      </c>
+      <c r="S64" t="n">
+        <v>2</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1.0172</v>
+      </c>
+      <c r="V64" t="n">
+        <v>5.1848</v>
+      </c>
+      <c r="W64" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="X64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>1037.72</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>BTCUSD</t>
+        </is>
+      </c>
+      <c r="AD64" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>68.06</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>supertrend_v6b_ultra</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>17</v>
+      </c>
+      <c r="D65" t="n">
+        <v>9</v>
+      </c>
+      <c r="E65" t="n">
+        <v>8</v>
+      </c>
+      <c r="F65" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-11.88</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="I65" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="J65" t="n">
+        <v>-111.87</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.8938</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-59.04</v>
+      </c>
+      <c r="M65" t="n">
+        <v>-5.81</v>
+      </c>
+      <c r="N65" t="n">
+        <v>-0.699</v>
+      </c>
+      <c r="O65" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P65" t="n">
+        <v>-13.984</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0.7945</v>
+      </c>
+      <c r="R65" t="n">
+        <v>-0.699</v>
+      </c>
+      <c r="S65" t="n">
+        <v>3</v>
+      </c>
+      <c r="T65" t="n">
+        <v>4</v>
+      </c>
+      <c r="U65" t="n">
+        <v>-0.08989999999999999</v>
+      </c>
+      <c r="V65" t="n">
+        <v>-0.0682</v>
+      </c>
+      <c r="W65" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="X65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>988.12</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>DOGEUSD</t>
+        </is>
+      </c>
+      <c r="AD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>92.06</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>30.69</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>supertrend_v6b_ultra</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>15</v>
+      </c>
+      <c r="D66" t="n">
+        <v>8</v>
+      </c>
+      <c r="E66" t="n">
+        <v>7</v>
+      </c>
+      <c r="F66" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="I66" t="n">
+        <v>83.22</v>
+      </c>
+      <c r="J66" t="n">
+        <v>-85.81999999999999</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.9697</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-59.04</v>
+      </c>
+      <c r="M66" t="n">
+        <v>-5.81</v>
+      </c>
+      <c r="N66" t="n">
+        <v>-0.1733</v>
+      </c>
+      <c r="O66" t="n">
+        <v>10.4025</v>
+      </c>
+      <c r="P66" t="n">
+        <v>-12.26</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.8485</v>
+      </c>
+      <c r="R66" t="n">
+        <v>-0.1733</v>
+      </c>
+      <c r="S66" t="n">
+        <v>3</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>-0.0138</v>
+      </c>
+      <c r="V66" t="n">
+        <v>-0.0213</v>
+      </c>
+      <c r="W66" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="X66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>997.4</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>DOGEUSD</t>
+        </is>
+      </c>
+      <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>92.06</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>30.69</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>supertrend_v6b_ultra</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="n">
+        <v>50</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-9.31</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="I67" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="J67" t="n">
+        <v>-26.12</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.6437</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-41.76</v>
+      </c>
+      <c r="M67" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="N67" t="n">
+        <v>-4.6533</v>
+      </c>
+      <c r="O67" t="n">
+        <v>16.8137</v>
+      </c>
+      <c r="P67" t="n">
+        <v>-26.1204</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0.6437</v>
+      </c>
+      <c r="R67" t="n">
+        <v>-4.6533</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>-0.2201</v>
+      </c>
+      <c r="V67" t="n">
+        <v>-0.2555</v>
+      </c>
+      <c r="W67" t="n">
+        <v>275</v>
+      </c>
+      <c r="X67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>990.6900000000001</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>DOGEUSD</t>
+        </is>
+      </c>
+      <c r="AD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>95.73</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>supertrend_v6b_ultra</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>33</v>
+      </c>
+      <c r="D68" t="n">
+        <v>15</v>
+      </c>
+      <c r="E68" t="n">
+        <v>18</v>
+      </c>
+      <c r="F68" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-69.64</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-6.96</v>
+      </c>
+      <c r="I68" t="n">
+        <v>69.47</v>
+      </c>
+      <c r="J68" t="n">
+        <v>-139.11</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.4994</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-83.61</v>
+      </c>
+      <c r="M68" t="n">
+        <v>-8.33</v>
+      </c>
+      <c r="N68" t="n">
+        <v>-2.1102</v>
+      </c>
+      <c r="O68" t="n">
+        <v>4.6315</v>
+      </c>
+      <c r="P68" t="n">
+        <v>-7.7284</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.5993000000000001</v>
+      </c>
+      <c r="R68" t="n">
+        <v>-2.1102</v>
+      </c>
+      <c r="S68" t="n">
+        <v>3</v>
+      </c>
+      <c r="T68" t="n">
+        <v>4</v>
+      </c>
+      <c r="U68" t="n">
+        <v>-0.8784</v>
+      </c>
+      <c r="V68" t="n">
+        <v>-0.2786</v>
+      </c>
+      <c r="W68" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="X68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>930.36</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>ETHUSD</t>
+        </is>
+      </c>
+      <c r="AD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>supertrend_v6b_ultra</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>25</v>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="n">
+        <v>15</v>
+      </c>
+      <c r="F69" t="n">
+        <v>40</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-33.28</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="I69" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="J69" t="n">
+        <v>-89.42</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.6278</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-47.42</v>
+      </c>
+      <c r="M69" t="n">
+        <v>-4.72</v>
+      </c>
+      <c r="N69" t="n">
+        <v>-1.3311</v>
+      </c>
+      <c r="O69" t="n">
+        <v>5.6139</v>
+      </c>
+      <c r="P69" t="n">
+        <v>-5.9611</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0.9418</v>
+      </c>
+      <c r="R69" t="n">
+        <v>-1.3311</v>
+      </c>
+      <c r="S69" t="n">
+        <v>3</v>
+      </c>
+      <c r="T69" t="n">
+        <v>4</v>
+      </c>
+      <c r="U69" t="n">
+        <v>-0.6411</v>
+      </c>
+      <c r="V69" t="n">
+        <v>-0.3355</v>
+      </c>
+      <c r="W69" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="X69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>966.72</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>ETHUSD</t>
+        </is>
+      </c>
+      <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>94.33</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>supertrend_v6b_ultra</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>8</v>
+      </c>
+      <c r="D70" t="n">
+        <v>5</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-37.61</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-3.76</v>
+      </c>
+      <c r="I70" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-51.41</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-61.08</v>
+      </c>
+      <c r="M70" t="n">
+        <v>-6.03</v>
+      </c>
+      <c r="N70" t="n">
+        <v>-4.7016</v>
+      </c>
+      <c r="O70" t="n">
+        <v>2.7585</v>
+      </c>
+      <c r="P70" t="n">
+        <v>-17.135</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="R70" t="n">
+        <v>-4.7016</v>
+      </c>
+      <c r="S70" t="n">
+        <v>3</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>-1.3046</v>
+      </c>
+      <c r="V70" t="n">
+        <v>-0.6927</v>
+      </c>
+      <c r="W70" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="X70" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>962.39</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>-4.18</v>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>ETHUSD</t>
+        </is>
+      </c>
+      <c r="AD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>supertrend_v6b_ultra</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>19</v>
+      </c>
+      <c r="D71" t="n">
+        <v>12</v>
+      </c>
+      <c r="E71" t="n">
+        <v>7</v>
+      </c>
+      <c r="F71" t="n">
+        <v>63.16</v>
+      </c>
+      <c r="G71" t="n">
+        <v>114.65</v>
+      </c>
+      <c r="H71" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="I71" t="n">
+        <v>238.35</v>
+      </c>
+      <c r="J71" t="n">
+        <v>-123.7</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1.9269</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-64.28</v>
+      </c>
+      <c r="M71" t="n">
+        <v>-6.22</v>
+      </c>
+      <c r="N71" t="n">
+        <v>6.0344</v>
+      </c>
+      <c r="O71" t="n">
+        <v>19.8625</v>
+      </c>
+      <c r="P71" t="n">
+        <v>-17.6709</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1.124</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6.0344</v>
+      </c>
+      <c r="S71" t="n">
+        <v>7</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0.6141</v>
+      </c>
+      <c r="W71" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="X71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>1114.65</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>SOLUSD</t>
+        </is>
+      </c>
+      <c r="AD71" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>91.20999999999999</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>supertrend_v6b_ultra</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>17</v>
+      </c>
+      <c r="D72" t="n">
+        <v>11</v>
+      </c>
+      <c r="E72" t="n">
+        <v>6</v>
+      </c>
+      <c r="F72" t="n">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="G72" t="n">
+        <v>137.06</v>
+      </c>
+      <c r="H72" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="I72" t="n">
+        <v>228.32</v>
+      </c>
+      <c r="J72" t="n">
+        <v>-91.26000000000001</v>
+      </c>
+      <c r="K72" t="n">
+        <v>2.5018</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-64.28</v>
+      </c>
+      <c r="M72" t="n">
+        <v>-6.22</v>
+      </c>
+      <c r="N72" t="n">
+        <v>8.062200000000001</v>
+      </c>
+      <c r="O72" t="n">
+        <v>20.7562</v>
+      </c>
+      <c r="P72" t="n">
+        <v>-15.2101</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1.3646</v>
+      </c>
+      <c r="R72" t="n">
+        <v>8.062200000000001</v>
+      </c>
+      <c r="S72" t="n">
+        <v>7</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1.0488</v>
+      </c>
+      <c r="W72" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="X72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>1137.06</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>SOLUSD</t>
+        </is>
+      </c>
+      <c r="AD72" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>91.20999999999999</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>44.23</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>supertrend_v6b_ultra</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>50</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-19.7</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="I73" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-28.53</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-31.91</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="N73" t="n">
+        <v>-9.851599999999999</v>
+      </c>
+      <c r="O73" t="n">
+        <v>8.8232</v>
+      </c>
+      <c r="P73" t="n">
+        <v>-28.5264</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="R73" t="n">
+        <v>-9.851599999999999</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>-0.5526</v>
+      </c>
+      <c r="V73" t="n">
+        <v>-0.6941000000000001</v>
+      </c>
+      <c r="W73" t="n">
+        <v>50</v>
+      </c>
+      <c r="X73" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>980.3</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>SOLUSD</t>
+        </is>
+      </c>
+      <c r="AD73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>supertrend_v7a_rsi_entry</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>8</v>
+      </c>
+      <c r="D74" t="n">
+        <v>5</v>
+      </c>
+      <c r="E74" t="n">
+        <v>3</v>
+      </c>
+      <c r="F74" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G74" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I74" t="n">
+        <v>29.87</v>
+      </c>
+      <c r="J74" t="n">
+        <v>-18.84</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1.5857</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-25.12</v>
+      </c>
+      <c r="M74" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="N74" t="n">
+        <v>1.379</v>
+      </c>
+      <c r="O74" t="n">
+        <v>5.9737</v>
+      </c>
+      <c r="P74" t="n">
+        <v>-6.2789</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0.9514</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1.379</v>
+      </c>
+      <c r="S74" t="n">
+        <v>2</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0.1509</v>
+      </c>
+      <c r="W74" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="X74" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1011.03</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>BTCUSD</t>
+        </is>
+      </c>
+      <c r="AD74" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>99.08</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>supertrend_v7a_rsi_entry</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" t="n">
+        <v>50</v>
+      </c>
+      <c r="G75" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I75" t="n">
+        <v>26.04</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-18.84</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1.3826</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-23.84</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1.2012</v>
+      </c>
+      <c r="O75" t="n">
+        <v>8.6812</v>
+      </c>
+      <c r="P75" t="n">
+        <v>-6.2789</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1.3826</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1.2012</v>
+      </c>
+      <c r="S75" t="n">
+        <v>2</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0.1485</v>
+      </c>
+      <c r="W75" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1007.21</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>BTCUSD</t>
+        </is>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>99.34999999999999</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>supertrend_v7a_rsi_entry</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" t="n">
+        <v>2</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>100</v>
+      </c>
+      <c r="G76" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I76" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J76" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>3797.568</v>
+      </c>
+      <c r="L76" t="n">
+        <v>-3.42</v>
+      </c>
+      <c r="M76" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="N76" t="n">
+        <v>1.8988</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1.8988</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1.8988</v>
+      </c>
+      <c r="S76" t="n">
+        <v>2</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2.4647</v>
+      </c>
+      <c r="V76" t="n">
+        <v>1.2364</v>
+      </c>
+      <c r="W76" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="X76" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>1003.8</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>BTCUSD</t>
+        </is>
+      </c>
+      <c r="AD76" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>47.21</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>supertrend_v7a_rsi_entry</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>5</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E77" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" t="n">
+        <v>60</v>
+      </c>
+      <c r="G77" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="I77" t="n">
+        <v>43.11</v>
+      </c>
+      <c r="J77" t="n">
+        <v>-16.41</v>
+      </c>
+      <c r="K77" t="n">
+        <v>2.6266</v>
+      </c>
+      <c r="L77" t="n">
+        <v>-24.57</v>
+      </c>
+      <c r="M77" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="N77" t="n">
+        <v>5.3392</v>
+      </c>
+      <c r="O77" t="n">
+        <v>14.3693</v>
+      </c>
+      <c r="P77" t="n">
+        <v>-8.206</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>1.7511</v>
+      </c>
+      <c r="R77" t="n">
+        <v>5.3392</v>
+      </c>
+      <c r="S77" t="n">
+        <v>3</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0.4897</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="W77" t="n">
+        <v>187</v>
+      </c>
+      <c r="X77" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>1026.7</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>DOGEUSD</t>
+        </is>
+      </c>
+      <c r="AD77" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>37.39</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>supertrend_v7a_rsi_entry</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>4</v>
+      </c>
+      <c r="D78" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" t="n">
+        <v>50</v>
+      </c>
+      <c r="G78" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I78" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="J78" t="n">
+        <v>-16.41</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1.5922</v>
+      </c>
+      <c r="L78" t="n">
+        <v>-18.24</v>
+      </c>
+      <c r="M78" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="N78" t="n">
+        <v>2.4297</v>
+      </c>
+      <c r="O78" t="n">
+        <v>13.0654</v>
+      </c>
+      <c r="P78" t="n">
+        <v>-8.206</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1.5922</v>
+      </c>
+      <c r="R78" t="n">
+        <v>2.4297</v>
+      </c>
+      <c r="S78" t="n">
+        <v>2</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0.2371</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0.2538</v>
+      </c>
+      <c r="W78" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="X78" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>1009.72</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>DOGEUSD</t>
+        </is>
+      </c>
+      <c r="AD78" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>36.31</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>supertrend_v7a_rsi_entry</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>100</v>
+      </c>
+      <c r="G79" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I79" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="J79" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>16813.7441</v>
+      </c>
+      <c r="L79" t="n">
+        <v>-24.33</v>
+      </c>
+      <c r="M79" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="N79" t="n">
+        <v>16.8137</v>
+      </c>
+      <c r="O79" t="n">
+        <v>16.8137</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>16.8137</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>17.7375</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0.7675</v>
+      </c>
+      <c r="W79" t="n">
+        <v>510</v>
+      </c>
+      <c r="X79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>1016.81</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>DOGEUSD</t>
+        </is>
+      </c>
+      <c r="AD79" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>42.19</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>supertrend_v7a_rsi_entry</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>7</v>
+      </c>
+      <c r="D80" t="n">
+        <v>4</v>
+      </c>
+      <c r="E80" t="n">
+        <v>3</v>
+      </c>
+      <c r="F80" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="G80" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="I80" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="J80" t="n">
+        <v>-29.69</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="L80" t="n">
+        <v>-27.15</v>
+      </c>
+      <c r="M80" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="N80" t="n">
+        <v>-0.0922</v>
+      </c>
+      <c r="O80" t="n">
+        <v>7.2607</v>
+      </c>
+      <c r="P80" t="n">
+        <v>-9.896000000000001</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0.7337</v>
+      </c>
+      <c r="R80" t="n">
+        <v>-0.0922</v>
+      </c>
+      <c r="S80" t="n">
+        <v>3</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>-0.0081</v>
+      </c>
+      <c r="V80" t="n">
+        <v>-0.0081</v>
+      </c>
+      <c r="W80" t="n">
+        <v>55</v>
+      </c>
+      <c r="X80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>999.35</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>ETHUSD</t>
+        </is>
+      </c>
+      <c r="AD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>32.88</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>supertrend_v7a_rsi_entry</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>6</v>
+      </c>
+      <c r="D81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="G81" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I81" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="J81" t="n">
+        <v>-16.64</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1.7454</v>
+      </c>
+      <c r="L81" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="M81" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="N81" t="n">
+        <v>2.0672</v>
+      </c>
+      <c r="O81" t="n">
+        <v>7.2607</v>
+      </c>
+      <c r="P81" t="n">
+        <v>-8.319800000000001</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0.8727</v>
+      </c>
+      <c r="R81" t="n">
+        <v>2.0672</v>
+      </c>
+      <c r="S81" t="n">
+        <v>3</v>
+      </c>
+      <c r="T81" t="n">
+        <v>1</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0.4069</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0.4299</v>
+      </c>
+      <c r="W81" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="X81" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>1012.4</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>ETHUSD</t>
+        </is>
+      </c>
+      <c r="AD81" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>38.31</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>supertrend_v7a_rsi_entry</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>-12.89</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>-12.89</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>-12.89</v>
+      </c>
+      <c r="M82" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="N82" t="n">
+        <v>-12.8886</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>-12.8886</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>-12.8886</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" t="n">
+        <v>-13.5968</v>
+      </c>
+      <c r="V82" t="n">
+        <v>-1.1107</v>
+      </c>
+      <c r="W82" t="n">
+        <v>35</v>
+      </c>
+      <c r="X82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>987.11</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>ETHUSD</t>
+        </is>
+      </c>
+      <c r="AD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>supertrend_v7a_rsi_entry</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>5</v>
+      </c>
+      <c r="D83" t="n">
+        <v>3</v>
+      </c>
+      <c r="E83" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" t="n">
+        <v>60</v>
+      </c>
+      <c r="G83" t="n">
+        <v>156.76</v>
+      </c>
+      <c r="H83" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="I83" t="n">
+        <v>199.81</v>
+      </c>
+      <c r="J83" t="n">
+        <v>-43.05</v>
+      </c>
+      <c r="K83" t="n">
+        <v>4.6412</v>
+      </c>
+      <c r="L83" t="n">
+        <v>-47.09</v>
+      </c>
+      <c r="M83" t="n">
+        <v>-4.17</v>
+      </c>
+      <c r="N83" t="n">
+        <v>31.3521</v>
+      </c>
+      <c r="O83" t="n">
+        <v>66.60429999999999</v>
+      </c>
+      <c r="P83" t="n">
+        <v>-21.5262</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>3.0941</v>
+      </c>
+      <c r="R83" t="n">
+        <v>31.3521</v>
+      </c>
+      <c r="S83" t="n">
+        <v>2</v>
+      </c>
+      <c r="T83" t="n">
+        <v>1</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0.5083</v>
+      </c>
+      <c r="V83" t="n">
+        <v>1.2536</v>
+      </c>
+      <c r="W83" t="n">
+        <v>51</v>
+      </c>
+      <c r="X83" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>1156.76</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>SOLUSD</t>
+        </is>
+      </c>
+      <c r="AD83" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>95.48</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>supertrend_v7a_rsi_entry</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>3</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="G84" t="n">
+        <v>180.01</v>
+      </c>
+      <c r="H84" t="n">
+        <v>18</v>
+      </c>
+      <c r="I84" t="n">
+        <v>189.4</v>
+      </c>
+      <c r="J84" t="n">
+        <v>-9.390000000000001</v>
+      </c>
+      <c r="K84" t="n">
+        <v>20.1688</v>
+      </c>
+      <c r="L84" t="n">
+        <v>-47.09</v>
+      </c>
+      <c r="M84" t="n">
+        <v>-4.17</v>
+      </c>
+      <c r="N84" t="n">
+        <v>60.0036</v>
+      </c>
+      <c r="O84" t="n">
+        <v>94.7008</v>
+      </c>
+      <c r="P84" t="n">
+        <v>-9.3908</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>10.0844</v>
+      </c>
+      <c r="R84" t="n">
+        <v>60.0036</v>
+      </c>
+      <c r="S84" t="n">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0.7164</v>
+      </c>
+      <c r="V84" t="n">
+        <v>2.0568</v>
+      </c>
+      <c r="W84" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="X84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>1180.01</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>SOLUSD</t>
+        </is>
+      </c>
+      <c r="AD84" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>68.56</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>95.48</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>supertrend_v7a_rsi_entry</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>50</v>
+      </c>
+      <c r="G85" t="n">
+        <v>-19.7</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="I85" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="J85" t="n">
+        <v>-28.53</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="L85" t="n">
+        <v>-31.91</v>
+      </c>
+      <c r="M85" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="N85" t="n">
+        <v>-9.851599999999999</v>
+      </c>
+      <c r="O85" t="n">
+        <v>8.8232</v>
+      </c>
+      <c r="P85" t="n">
+        <v>-28.5264</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="R85" t="n">
+        <v>-9.851599999999999</v>
+      </c>
+      <c r="S85" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>1</v>
+      </c>
+      <c r="U85" t="n">
+        <v>-0.5526</v>
+      </c>
+      <c r="V85" t="n">
+        <v>-0.6941000000000001</v>
+      </c>
+      <c r="W85" t="n">
+        <v>50</v>
+      </c>
+      <c r="X85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>980.3</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>SOLUSD</t>
+        </is>
+      </c>
+      <c r="AD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>supertrend_v7b_no_stop</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>27</v>
+      </c>
+      <c r="D86" t="n">
+        <v>15</v>
+      </c>
+      <c r="E86" t="n">
+        <v>12</v>
+      </c>
+      <c r="F86" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="G86" t="n">
+        <v>46.84</v>
+      </c>
+      <c r="H86" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="I86" t="n">
+        <v>118.03</v>
+      </c>
+      <c r="J86" t="n">
+        <v>-71.19</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1.658</v>
+      </c>
+      <c r="L86" t="n">
+        <v>-48.25</v>
+      </c>
+      <c r="M86" t="n">
+        <v>-4.72</v>
+      </c>
+      <c r="N86" t="n">
+        <v>1.7348</v>
+      </c>
+      <c r="O86" t="n">
+        <v>7.8685</v>
+      </c>
+      <c r="P86" t="n">
+        <v>-5.9324</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>1.3264</v>
+      </c>
+      <c r="R86" t="n">
+        <v>1.7348</v>
+      </c>
+      <c r="S86" t="n">
+        <v>4</v>
+      </c>
+      <c r="T86" t="n">
+        <v>3</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0.4648</v>
+      </c>
+      <c r="V86" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="W86" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="X86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>1046.84</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>BTCUSD</t>
+        </is>
+      </c>
+      <c r="AD86" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>94.33</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>supertrend_v7b_no_stop</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>21</v>
+      </c>
+      <c r="D87" t="n">
+        <v>12</v>
+      </c>
+      <c r="E87" t="n">
+        <v>9</v>
+      </c>
+      <c r="F87" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="G87" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I87" t="n">
+        <v>75.23999999999999</v>
+      </c>
+      <c r="J87" t="n">
+        <v>-63.02</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1.1939</v>
+      </c>
+      <c r="L87" t="n">
+        <v>-48.25</v>
+      </c>
+      <c r="M87" t="n">
+        <v>-4.72</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="O87" t="n">
+        <v>6.2704</v>
+      </c>
+      <c r="P87" t="n">
+        <v>-7.0025</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0.8955</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="S87" t="n">
+        <v>4</v>
+      </c>
+      <c r="T87" t="n">
+        <v>3</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0.2025</v>
+      </c>
+      <c r="V87" t="n">
+        <v>0.1232</v>
+      </c>
+      <c r="W87" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="X87" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>1012.22</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>BTCUSD</t>
+        </is>
+      </c>
+      <c r="AD87" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>94.33</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>supertrend_v7b_no_stop</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>6</v>
+      </c>
+      <c r="D88" t="n">
+        <v>3</v>
+      </c>
+      <c r="E88" t="n">
+        <v>3</v>
+      </c>
+      <c r="F88" t="n">
+        <v>50</v>
+      </c>
+      <c r="G88" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="H88" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="I88" t="n">
+        <v>42.27</v>
+      </c>
+      <c r="J88" t="n">
+        <v>-8.07</v>
+      </c>
+      <c r="K88" t="n">
+        <v>5.2392</v>
+      </c>
+      <c r="L88" t="n">
+        <v>-11.47</v>
+      </c>
+      <c r="M88" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="N88" t="n">
+        <v>5.6997</v>
+      </c>
+      <c r="O88" t="n">
+        <v>14.0885</v>
+      </c>
+      <c r="P88" t="n">
+        <v>-2.6891</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>5.2392</v>
+      </c>
+      <c r="R88" t="n">
+        <v>5.6997</v>
+      </c>
+      <c r="S88" t="n">
+        <v>2</v>
+      </c>
+      <c r="T88" t="n">
+        <v>3</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0.9069</v>
+      </c>
+      <c r="V88" t="n">
+        <v>3.3195</v>
+      </c>
+      <c r="W88" t="n">
+        <v>155</v>
+      </c>
+      <c r="X88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>1034.2</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>BTCUSD</t>
+        </is>
+      </c>
+      <c r="AD88" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>67.93000000000001</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>supertrend_v7b_no_stop</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>17</v>
+      </c>
+      <c r="D89" t="n">
+        <v>9</v>
+      </c>
+      <c r="E89" t="n">
+        <v>8</v>
+      </c>
+      <c r="F89" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="G89" t="n">
+        <v>35.41</v>
+      </c>
+      <c r="H89" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="I89" t="n">
+        <v>187.18</v>
+      </c>
+      <c r="J89" t="n">
+        <v>-151.78</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1.2333</v>
+      </c>
+      <c r="L89" t="n">
+        <v>-72.48999999999999</v>
+      </c>
+      <c r="M89" t="n">
+        <v>-7.15</v>
+      </c>
+      <c r="N89" t="n">
+        <v>2.0827</v>
+      </c>
+      <c r="O89" t="n">
+        <v>20.798</v>
+      </c>
+      <c r="P89" t="n">
+        <v>-18.9721</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>1.0962</v>
+      </c>
+      <c r="R89" t="n">
+        <v>2.0827</v>
+      </c>
+      <c r="S89" t="n">
+        <v>3</v>
+      </c>
+      <c r="T89" t="n">
+        <v>4</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="W89" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="X89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>1035.41</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>DOGEUSD</t>
+        </is>
+      </c>
+      <c r="AD89" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>89.27</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>supertrend_v7b_no_stop</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>15</v>
+      </c>
+      <c r="D90" t="n">
+        <v>8</v>
+      </c>
+      <c r="E90" t="n">
+        <v>7</v>
+      </c>
+      <c r="F90" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="G90" t="n">
+        <v>70.17</v>
+      </c>
+      <c r="H90" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="I90" t="n">
+        <v>177.05</v>
+      </c>
+      <c r="J90" t="n">
+        <v>-106.88</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1.6566</v>
+      </c>
+      <c r="L90" t="n">
+        <v>-72.48999999999999</v>
+      </c>
+      <c r="M90" t="n">
+        <v>-7.15</v>
+      </c>
+      <c r="N90" t="n">
+        <v>4.6783</v>
+      </c>
+      <c r="O90" t="n">
+        <v>22.1315</v>
+      </c>
+      <c r="P90" t="n">
+        <v>-15.2682</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>1.4495</v>
+      </c>
+      <c r="R90" t="n">
+        <v>4.6783</v>
+      </c>
+      <c r="S90" t="n">
+        <v>3</v>
+      </c>
+      <c r="T90" t="n">
+        <v>4</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="V90" t="n">
+        <v>0.4674</v>
+      </c>
+      <c r="W90" t="n">
+        <v>157.7</v>
+      </c>
+      <c r="X90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>1070.17</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>DOGEUSD</t>
+        </is>
+      </c>
+      <c r="AD90" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>89.27</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>36.06</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>supertrend_v7b_no_stop</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>50</v>
+      </c>
+      <c r="G91" t="n">
+        <v>-32.49</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="I91" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="J91" t="n">
+        <v>-41.96</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.2256</v>
+      </c>
+      <c r="L91" t="n">
+        <v>-64.95</v>
+      </c>
+      <c r="M91" t="n">
+        <v>-6.29</v>
+      </c>
+      <c r="N91" t="n">
+        <v>-16.2448</v>
+      </c>
+      <c r="O91" t="n">
+        <v>9.4658</v>
+      </c>
+      <c r="P91" t="n">
+        <v>-41.9555</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0.2256</v>
+      </c>
+      <c r="R91" t="n">
+        <v>-16.2448</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1</v>
+      </c>
+      <c r="T91" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" t="n">
+        <v>-0.6629</v>
+      </c>
+      <c r="V91" t="n">
+        <v>-0.5736</v>
+      </c>
+      <c r="W91" t="n">
+        <v>375</v>
+      </c>
+      <c r="X91" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>967.51</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>-3.61</v>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>DOGEUSD</t>
+        </is>
+      </c>
+      <c r="AD91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>91.06</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>supertrend_v7b_no_stop</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>33</v>
+      </c>
+      <c r="D92" t="n">
+        <v>21</v>
+      </c>
+      <c r="E92" t="n">
+        <v>12</v>
+      </c>
+      <c r="F92" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="G92" t="n">
+        <v>-32.6</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="I92" t="n">
+        <v>93.45999999999999</v>
+      </c>
+      <c r="J92" t="n">
+        <v>-126.06</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.7413999999999999</v>
+      </c>
+      <c r="L92" t="n">
+        <v>-92.55</v>
+      </c>
+      <c r="M92" t="n">
+        <v>-8.82</v>
+      </c>
+      <c r="N92" t="n">
+        <v>-0.9879</v>
+      </c>
+      <c r="O92" t="n">
+        <v>4.4505</v>
+      </c>
+      <c r="P92" t="n">
+        <v>-10.505</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="R92" t="n">
+        <v>-0.9879</v>
+      </c>
+      <c r="S92" t="n">
+        <v>7</v>
+      </c>
+      <c r="T92" t="n">
+        <v>3</v>
+      </c>
+      <c r="U92" t="n">
+        <v>-0.3025</v>
+      </c>
+      <c r="V92" t="n">
+        <v>-0.1232</v>
+      </c>
+      <c r="W92" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="X92" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>967.4</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>ETHUSD</t>
+        </is>
+      </c>
+      <c r="AD92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>85.79000000000001</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>supertrend_v7b_no_stop</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>25</v>
+      </c>
+      <c r="D93" t="n">
+        <v>16</v>
+      </c>
+      <c r="E93" t="n">
+        <v>9</v>
+      </c>
+      <c r="F93" t="n">
+        <v>64</v>
+      </c>
+      <c r="G93" t="n">
+        <v>35.96</v>
+      </c>
+      <c r="H93" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I93" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="J93" t="n">
+        <v>-43.38</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1.829</v>
+      </c>
+      <c r="L93" t="n">
+        <v>-29</v>
+      </c>
+      <c r="M93" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="N93" t="n">
+        <v>1.4386</v>
+      </c>
+      <c r="O93" t="n">
+        <v>4.9591</v>
+      </c>
+      <c r="P93" t="n">
+        <v>-4.8202</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>1.0288</v>
+      </c>
+      <c r="R93" t="n">
+        <v>1.4386</v>
+      </c>
+      <c r="S93" t="n">
+        <v>7</v>
+      </c>
+      <c r="T93" t="n">
+        <v>3</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0.7573</v>
+      </c>
+      <c r="V93" t="n">
+        <v>0.5927</v>
+      </c>
+      <c r="W93" t="n">
+        <v>143</v>
+      </c>
+      <c r="X93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>1035.96</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>ETHUSD</t>
+        </is>
+      </c>
+      <c r="AD93" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>39.87</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>supertrend_v7b_no_stop</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>8</v>
+      </c>
+      <c r="D94" t="n">
+        <v>5</v>
+      </c>
+      <c r="E94" t="n">
+        <v>3</v>
+      </c>
+      <c r="F94" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G94" t="n">
+        <v>-66.18000000000001</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-6.62</v>
+      </c>
+      <c r="I94" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="J94" t="n">
+        <v>-79.81</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.1707</v>
+      </c>
+      <c r="L94" t="n">
+        <v>-89.34</v>
+      </c>
+      <c r="M94" t="n">
+        <v>-8.82</v>
+      </c>
+      <c r="N94" t="n">
+        <v>-8.273</v>
+      </c>
+      <c r="O94" t="n">
+        <v>2.7248</v>
+      </c>
+      <c r="P94" t="n">
+        <v>-26.6027</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0.1024</v>
+      </c>
+      <c r="R94" t="n">
+        <v>-8.273</v>
+      </c>
+      <c r="S94" t="n">
+        <v>3</v>
+      </c>
+      <c r="T94" t="n">
+        <v>3</v>
+      </c>
+      <c r="U94" t="n">
+        <v>-1.5353</v>
+      </c>
+      <c r="V94" t="n">
+        <v>-0.8334</v>
+      </c>
+      <c r="W94" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="X94" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>933.8200000000001</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>-7.35</v>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>ETHUSD</t>
+        </is>
+      </c>
+      <c r="AD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>85.79000000000001</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>supertrend_v7b_no_stop</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>19</v>
+      </c>
+      <c r="D95" t="n">
+        <v>13</v>
+      </c>
+      <c r="E95" t="n">
+        <v>6</v>
+      </c>
+      <c r="F95" t="n">
+        <v>68.42</v>
+      </c>
+      <c r="G95" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="H95" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="I95" t="n">
+        <v>235.95</v>
+      </c>
+      <c r="J95" t="n">
+        <v>-170.64</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1.3827</v>
+      </c>
+      <c r="L95" t="n">
+        <v>-102.01</v>
+      </c>
+      <c r="M95" t="n">
+        <v>-9.880000000000001</v>
+      </c>
+      <c r="N95" t="n">
+        <v>3.4373</v>
+      </c>
+      <c r="O95" t="n">
+        <v>18.1502</v>
+      </c>
+      <c r="P95" t="n">
+        <v>-28.4406</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0.6382</v>
+      </c>
+      <c r="R95" t="n">
+        <v>3.4373</v>
+      </c>
+      <c r="S95" t="n">
+        <v>7</v>
+      </c>
+      <c r="T95" t="n">
+        <v>2</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0.2337</v>
+      </c>
+      <c r="V95" t="n">
+        <v>0.2204</v>
+      </c>
+      <c r="W95" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="X95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>1065.31</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>SOLUSD</t>
+        </is>
+      </c>
+      <c r="AD95" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>83.58</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>supertrend_v7b_no_stop</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>17</v>
+      </c>
+      <c r="D96" t="n">
+        <v>12</v>
+      </c>
+      <c r="E96" t="n">
+        <v>5</v>
+      </c>
+      <c r="F96" t="n">
+        <v>70.59</v>
+      </c>
+      <c r="G96" t="n">
+        <v>107.02</v>
+      </c>
+      <c r="H96" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I96" t="n">
+        <v>226.18</v>
+      </c>
+      <c r="J96" t="n">
+        <v>-119.17</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1.898</v>
+      </c>
+      <c r="L96" t="n">
+        <v>-102.01</v>
+      </c>
+      <c r="M96" t="n">
+        <v>-9.880000000000001</v>
+      </c>
+      <c r="N96" t="n">
+        <v>6.2952</v>
+      </c>
+      <c r="O96" t="n">
+        <v>18.8487</v>
+      </c>
+      <c r="P96" t="n">
+        <v>-23.8335</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0.7909</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6.2952</v>
+      </c>
+      <c r="S96" t="n">
+        <v>7</v>
+      </c>
+      <c r="T96" t="n">
+        <v>2</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0.4218</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="W96" t="n">
+        <v>125</v>
+      </c>
+      <c r="X96" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>1107.02</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>SOLUSD</t>
+        </is>
+      </c>
+      <c r="AD96" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>83.58</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>supertrend_v7b_no_stop</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>2</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" t="n">
+        <v>50</v>
+      </c>
+      <c r="G97" t="n">
+        <v>-37.68</v>
+      </c>
+      <c r="H97" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="I97" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="J97" t="n">
+        <v>-46.5</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.1897</v>
+      </c>
+      <c r="L97" t="n">
+        <v>-49.89</v>
+      </c>
+      <c r="M97" t="n">
+        <v>-4.93</v>
+      </c>
+      <c r="N97" t="n">
+        <v>-18.8385</v>
+      </c>
+      <c r="O97" t="n">
+        <v>8.8232</v>
+      </c>
+      <c r="P97" t="n">
+        <v>-46.5002</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0.1897</v>
+      </c>
+      <c r="R97" t="n">
+        <v>-18.8385</v>
+      </c>
+      <c r="S97" t="n">
+        <v>1</v>
+      </c>
+      <c r="T97" t="n">
+        <v>1</v>
+      </c>
+      <c r="U97" t="n">
+        <v>-0.7153</v>
+      </c>
+      <c r="V97" t="n">
+        <v>-0.8491</v>
+      </c>
+      <c r="W97" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="X97" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>962.3200000000001</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>-4.18</v>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>SOLUSD</t>
+        </is>
+      </c>
+      <c r="AD97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>supertrend_v7c_hard_only</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>27</v>
+      </c>
+      <c r="D98" t="n">
+        <v>15</v>
+      </c>
+      <c r="E98" t="n">
+        <v>12</v>
+      </c>
+      <c r="F98" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="G98" t="n">
+        <v>46.84</v>
+      </c>
+      <c r="H98" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="I98" t="n">
+        <v>118.03</v>
+      </c>
+      <c r="J98" t="n">
+        <v>-71.19</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1.658</v>
+      </c>
+      <c r="L98" t="n">
+        <v>-48.25</v>
+      </c>
+      <c r="M98" t="n">
+        <v>-4.72</v>
+      </c>
+      <c r="N98" t="n">
+        <v>1.7348</v>
+      </c>
+      <c r="O98" t="n">
+        <v>7.8685</v>
+      </c>
+      <c r="P98" t="n">
+        <v>-5.9324</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>1.3264</v>
+      </c>
+      <c r="R98" t="n">
+        <v>1.7348</v>
+      </c>
+      <c r="S98" t="n">
+        <v>4</v>
+      </c>
+      <c r="T98" t="n">
+        <v>3</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0.4648</v>
+      </c>
+      <c r="V98" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="W98" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="X98" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>1046.84</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>BTCUSD</t>
+        </is>
+      </c>
+      <c r="AD98" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>94.33</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>supertrend_v7c_hard_only</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>21</v>
+      </c>
+      <c r="D99" t="n">
+        <v>12</v>
+      </c>
+      <c r="E99" t="n">
+        <v>9</v>
+      </c>
+      <c r="F99" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="G99" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="H99" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I99" t="n">
+        <v>75.23999999999999</v>
+      </c>
+      <c r="J99" t="n">
+        <v>-63.02</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1.1939</v>
+      </c>
+      <c r="L99" t="n">
+        <v>-48.25</v>
+      </c>
+      <c r="M99" t="n">
+        <v>-4.72</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="O99" t="n">
+        <v>6.2704</v>
+      </c>
+      <c r="P99" t="n">
+        <v>-7.0025</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0.8955</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="S99" t="n">
+        <v>4</v>
+      </c>
+      <c r="T99" t="n">
+        <v>3</v>
+      </c>
+      <c r="U99" t="n">
+        <v>0.2025</v>
+      </c>
+      <c r="V99" t="n">
+        <v>0.1232</v>
+      </c>
+      <c r="W99" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="X99" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>1012.22</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>BTCUSD</t>
+        </is>
+      </c>
+      <c r="AD99" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>94.33</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>supertrend_v7c_hard_only</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>6</v>
+      </c>
+      <c r="D100" t="n">
+        <v>3</v>
+      </c>
+      <c r="E100" t="n">
+        <v>3</v>
+      </c>
+      <c r="F100" t="n">
+        <v>50</v>
+      </c>
+      <c r="G100" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="H100" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="I100" t="n">
+        <v>42.27</v>
+      </c>
+      <c r="J100" t="n">
+        <v>-8.07</v>
+      </c>
+      <c r="K100" t="n">
+        <v>5.2392</v>
+      </c>
+      <c r="L100" t="n">
+        <v>-11.47</v>
+      </c>
+      <c r="M100" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="N100" t="n">
+        <v>5.6997</v>
+      </c>
+      <c r="O100" t="n">
+        <v>14.0885</v>
+      </c>
+      <c r="P100" t="n">
+        <v>-2.6891</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>5.2392</v>
+      </c>
+      <c r="R100" t="n">
+        <v>5.6997</v>
+      </c>
+      <c r="S100" t="n">
+        <v>2</v>
+      </c>
+      <c r="T100" t="n">
+        <v>3</v>
+      </c>
+      <c r="U100" t="n">
+        <v>0.9069</v>
+      </c>
+      <c r="V100" t="n">
+        <v>3.3195</v>
+      </c>
+      <c r="W100" t="n">
+        <v>155</v>
+      </c>
+      <c r="X100" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>1034.2</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>BTCUSD</t>
+        </is>
+      </c>
+      <c r="AD100" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>67.93000000000001</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>supertrend_v7c_hard_only</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>17</v>
+      </c>
+      <c r="D101" t="n">
+        <v>9</v>
+      </c>
+      <c r="E101" t="n">
+        <v>8</v>
+      </c>
+      <c r="F101" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="G101" t="n">
+        <v>35.41</v>
+      </c>
+      <c r="H101" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="I101" t="n">
+        <v>187.18</v>
+      </c>
+      <c r="J101" t="n">
+        <v>-151.78</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1.2333</v>
+      </c>
+      <c r="L101" t="n">
+        <v>-72.48999999999999</v>
+      </c>
+      <c r="M101" t="n">
+        <v>-7.15</v>
+      </c>
+      <c r="N101" t="n">
+        <v>2.0827</v>
+      </c>
+      <c r="O101" t="n">
+        <v>20.798</v>
+      </c>
+      <c r="P101" t="n">
+        <v>-18.9721</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>1.0962</v>
+      </c>
+      <c r="R101" t="n">
+        <v>2.0827</v>
+      </c>
+      <c r="S101" t="n">
+        <v>3</v>
+      </c>
+      <c r="T101" t="n">
+        <v>4</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="V101" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="W101" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="X101" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>1035.41</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>DOGEUSD</t>
+        </is>
+      </c>
+      <c r="AD101" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>89.27</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>supertrend_v7c_hard_only</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>15</v>
+      </c>
+      <c r="D102" t="n">
+        <v>8</v>
+      </c>
+      <c r="E102" t="n">
+        <v>7</v>
+      </c>
+      <c r="F102" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="G102" t="n">
+        <v>70.17</v>
+      </c>
+      <c r="H102" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="I102" t="n">
+        <v>177.05</v>
+      </c>
+      <c r="J102" t="n">
+        <v>-106.88</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1.6566</v>
+      </c>
+      <c r="L102" t="n">
+        <v>-72.48999999999999</v>
+      </c>
+      <c r="M102" t="n">
+        <v>-7.15</v>
+      </c>
+      <c r="N102" t="n">
+        <v>4.6783</v>
+      </c>
+      <c r="O102" t="n">
+        <v>22.1315</v>
+      </c>
+      <c r="P102" t="n">
+        <v>-15.2682</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>1.4495</v>
+      </c>
+      <c r="R102" t="n">
+        <v>4.6783</v>
+      </c>
+      <c r="S102" t="n">
+        <v>3</v>
+      </c>
+      <c r="T102" t="n">
+        <v>4</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="V102" t="n">
+        <v>0.4674</v>
+      </c>
+      <c r="W102" t="n">
+        <v>157.7</v>
+      </c>
+      <c r="X102" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>1070.17</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>DOGEUSD</t>
+        </is>
+      </c>
+      <c r="AD102" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>89.27</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>36.06</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>supertrend_v7c_hard_only</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" t="n">
+        <v>50</v>
+      </c>
+      <c r="G103" t="n">
+        <v>-32.49</v>
+      </c>
+      <c r="H103" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="I103" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="J103" t="n">
+        <v>-41.96</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0.2256</v>
+      </c>
+      <c r="L103" t="n">
+        <v>-64.95</v>
+      </c>
+      <c r="M103" t="n">
+        <v>-6.29</v>
+      </c>
+      <c r="N103" t="n">
+        <v>-16.2448</v>
+      </c>
+      <c r="O103" t="n">
+        <v>9.4658</v>
+      </c>
+      <c r="P103" t="n">
+        <v>-41.9555</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0.2256</v>
+      </c>
+      <c r="R103" t="n">
+        <v>-16.2448</v>
+      </c>
+      <c r="S103" t="n">
+        <v>1</v>
+      </c>
+      <c r="T103" t="n">
+        <v>1</v>
+      </c>
+      <c r="U103" t="n">
+        <v>-0.6629</v>
+      </c>
+      <c r="V103" t="n">
+        <v>-0.5736</v>
+      </c>
+      <c r="W103" t="n">
+        <v>375</v>
+      </c>
+      <c r="X103" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>967.51</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>-3.61</v>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>DOGEUSD</t>
+        </is>
+      </c>
+      <c r="AD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>91.06</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>supertrend_v7c_hard_only</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>33</v>
+      </c>
+      <c r="D104" t="n">
+        <v>21</v>
+      </c>
+      <c r="E104" t="n">
+        <v>12</v>
+      </c>
+      <c r="F104" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="G104" t="n">
+        <v>-32.6</v>
+      </c>
+      <c r="H104" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="I104" t="n">
+        <v>93.45999999999999</v>
+      </c>
+      <c r="J104" t="n">
+        <v>-126.06</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0.7413999999999999</v>
+      </c>
+      <c r="L104" t="n">
+        <v>-92.55</v>
+      </c>
+      <c r="M104" t="n">
+        <v>-8.82</v>
+      </c>
+      <c r="N104" t="n">
+        <v>-0.9879</v>
+      </c>
+      <c r="O104" t="n">
+        <v>4.4505</v>
+      </c>
+      <c r="P104" t="n">
+        <v>-10.505</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="R104" t="n">
+        <v>-0.9879</v>
+      </c>
+      <c r="S104" t="n">
+        <v>7</v>
+      </c>
+      <c r="T104" t="n">
+        <v>3</v>
+      </c>
+      <c r="U104" t="n">
+        <v>-0.3025</v>
+      </c>
+      <c r="V104" t="n">
+        <v>-0.1232</v>
+      </c>
+      <c r="W104" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="X104" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>967.4</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>ETHUSD</t>
+        </is>
+      </c>
+      <c r="AD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>85.79000000000001</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>supertrend_v7c_hard_only</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>25</v>
+      </c>
+      <c r="D105" t="n">
+        <v>16</v>
+      </c>
+      <c r="E105" t="n">
+        <v>9</v>
+      </c>
+      <c r="F105" t="n">
+        <v>64</v>
+      </c>
+      <c r="G105" t="n">
+        <v>35.96</v>
+      </c>
+      <c r="H105" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I105" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="J105" t="n">
+        <v>-43.38</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1.829</v>
+      </c>
+      <c r="L105" t="n">
+        <v>-29</v>
+      </c>
+      <c r="M105" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="N105" t="n">
+        <v>1.4386</v>
+      </c>
+      <c r="O105" t="n">
+        <v>4.9591</v>
+      </c>
+      <c r="P105" t="n">
+        <v>-4.8202</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>1.0288</v>
+      </c>
+      <c r="R105" t="n">
+        <v>1.4386</v>
+      </c>
+      <c r="S105" t="n">
+        <v>7</v>
+      </c>
+      <c r="T105" t="n">
+        <v>3</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0.7573</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0.5927</v>
+      </c>
+      <c r="W105" t="n">
+        <v>143</v>
+      </c>
+      <c r="X105" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>1035.96</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>ETHUSD</t>
+        </is>
+      </c>
+      <c r="AD105" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>39.87</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>supertrend_v7c_hard_only</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>8</v>
+      </c>
+      <c r="D106" t="n">
+        <v>5</v>
+      </c>
+      <c r="E106" t="n">
+        <v>3</v>
+      </c>
+      <c r="F106" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G106" t="n">
+        <v>-66.18000000000001</v>
+      </c>
+      <c r="H106" t="n">
+        <v>-6.62</v>
+      </c>
+      <c r="I106" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="J106" t="n">
+        <v>-79.81</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0.1707</v>
+      </c>
+      <c r="L106" t="n">
+        <v>-89.34</v>
+      </c>
+      <c r="M106" t="n">
+        <v>-8.82</v>
+      </c>
+      <c r="N106" t="n">
+        <v>-8.273</v>
+      </c>
+      <c r="O106" t="n">
+        <v>2.7248</v>
+      </c>
+      <c r="P106" t="n">
+        <v>-26.6027</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0.1024</v>
+      </c>
+      <c r="R106" t="n">
+        <v>-8.273</v>
+      </c>
+      <c r="S106" t="n">
+        <v>3</v>
+      </c>
+      <c r="T106" t="n">
+        <v>3</v>
+      </c>
+      <c r="U106" t="n">
+        <v>-1.5353</v>
+      </c>
+      <c r="V106" t="n">
+        <v>-0.8334</v>
+      </c>
+      <c r="W106" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="X106" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>933.8200000000001</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>-7.35</v>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>ETHUSD</t>
+        </is>
+      </c>
+      <c r="AD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>85.79000000000001</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>supertrend_v7c_hard_only</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>19</v>
+      </c>
+      <c r="D107" t="n">
+        <v>13</v>
+      </c>
+      <c r="E107" t="n">
+        <v>6</v>
+      </c>
+      <c r="F107" t="n">
+        <v>68.42</v>
+      </c>
+      <c r="G107" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="H107" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="I107" t="n">
+        <v>235.95</v>
+      </c>
+      <c r="J107" t="n">
+        <v>-170.64</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1.3827</v>
+      </c>
+      <c r="L107" t="n">
+        <v>-102.01</v>
+      </c>
+      <c r="M107" t="n">
+        <v>-9.880000000000001</v>
+      </c>
+      <c r="N107" t="n">
+        <v>3.4373</v>
+      </c>
+      <c r="O107" t="n">
+        <v>18.1502</v>
+      </c>
+      <c r="P107" t="n">
+        <v>-28.4406</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0.6382</v>
+      </c>
+      <c r="R107" t="n">
+        <v>3.4373</v>
+      </c>
+      <c r="S107" t="n">
+        <v>7</v>
+      </c>
+      <c r="T107" t="n">
+        <v>2</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0.2337</v>
+      </c>
+      <c r="V107" t="n">
+        <v>0.2204</v>
+      </c>
+      <c r="W107" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="X107" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>1065.31</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>SOLUSD</t>
+        </is>
+      </c>
+      <c r="AD107" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>83.58</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>supertrend_v7c_hard_only</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>17</v>
+      </c>
+      <c r="D108" t="n">
+        <v>12</v>
+      </c>
+      <c r="E108" t="n">
+        <v>5</v>
+      </c>
+      <c r="F108" t="n">
+        <v>70.59</v>
+      </c>
+      <c r="G108" t="n">
+        <v>107.02</v>
+      </c>
+      <c r="H108" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I108" t="n">
+        <v>226.18</v>
+      </c>
+      <c r="J108" t="n">
+        <v>-119.17</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1.898</v>
+      </c>
+      <c r="L108" t="n">
+        <v>-102.01</v>
+      </c>
+      <c r="M108" t="n">
+        <v>-9.880000000000001</v>
+      </c>
+      <c r="N108" t="n">
+        <v>6.2952</v>
+      </c>
+      <c r="O108" t="n">
+        <v>18.8487</v>
+      </c>
+      <c r="P108" t="n">
+        <v>-23.8335</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0.7909</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6.2952</v>
+      </c>
+      <c r="S108" t="n">
+        <v>7</v>
+      </c>
+      <c r="T108" t="n">
+        <v>2</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0.4218</v>
+      </c>
+      <c r="V108" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="W108" t="n">
+        <v>125</v>
+      </c>
+      <c r="X108" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>1107.02</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>SOLUSD</t>
+        </is>
+      </c>
+      <c r="AD108" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>83.58</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>supertrend_v7c_hard_only</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>2</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" t="n">
+        <v>50</v>
+      </c>
+      <c r="G109" t="n">
+        <v>-37.68</v>
+      </c>
+      <c r="H109" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="I109" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="J109" t="n">
+        <v>-46.5</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.1897</v>
+      </c>
+      <c r="L109" t="n">
+        <v>-49.89</v>
+      </c>
+      <c r="M109" t="n">
+        <v>-4.93</v>
+      </c>
+      <c r="N109" t="n">
+        <v>-18.8385</v>
+      </c>
+      <c r="O109" t="n">
+        <v>8.8232</v>
+      </c>
+      <c r="P109" t="n">
+        <v>-46.5002</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0.1897</v>
+      </c>
+      <c r="R109" t="n">
+        <v>-18.8385</v>
+      </c>
+      <c r="S109" t="n">
+        <v>1</v>
+      </c>
+      <c r="T109" t="n">
+        <v>1</v>
+      </c>
+      <c r="U109" t="n">
+        <v>-0.7153</v>
+      </c>
+      <c r="V109" t="n">
+        <v>-0.8491</v>
+      </c>
+      <c r="W109" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="X109" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>962.3200000000001</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>-4.18</v>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>SOLUSD</t>
+        </is>
+      </c>
+      <c r="AD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>supertrend_v7d_half_equity</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>27</v>
+      </c>
+      <c r="D110" t="n">
+        <v>13</v>
+      </c>
+      <c r="E110" t="n">
+        <v>14</v>
+      </c>
+      <c r="F110" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="G110" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="H110" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="I110" t="n">
+        <v>57.67</v>
+      </c>
+      <c r="J110" t="n">
+        <v>-29.76</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1.9376</v>
+      </c>
+      <c r="L110" t="n">
+        <v>-17.38</v>
+      </c>
+      <c r="M110" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="N110" t="n">
+        <v>1.0336</v>
+      </c>
+      <c r="O110" t="n">
+        <v>4.4362</v>
+      </c>
+      <c r="P110" t="n">
+        <v>-2.126</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>2.0866</v>
+      </c>
+      <c r="R110" t="n">
+        <v>1.0336</v>
+      </c>
+      <c r="S110" t="n">
+        <v>3</v>
+      </c>
+      <c r="T110" t="n">
+        <v>3</v>
+      </c>
+      <c r="U110" t="n">
+        <v>0.5794</v>
+      </c>
+      <c r="V110" t="n">
+        <v>0.5387</v>
+      </c>
+      <c r="W110" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="X110" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>1027.91</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>BTCUSD</t>
+        </is>
+      </c>
+      <c r="AD110" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>39.63</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>supertrend_v7d_half_equity</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>21</v>
+      </c>
+      <c r="D111" t="n">
+        <v>10</v>
+      </c>
+      <c r="E111" t="n">
+        <v>11</v>
+      </c>
+      <c r="F111" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="G111" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I111" t="n">
+        <v>36.27</v>
+      </c>
+      <c r="J111" t="n">
+        <v>-27.4</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1.3237</v>
+      </c>
+      <c r="L111" t="n">
+        <v>-17.38</v>
+      </c>
+      <c r="M111" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="O111" t="n">
+        <v>3.6268</v>
+      </c>
+      <c r="P111" t="n">
+        <v>-2.4908</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>1.4561</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="S111" t="n">
+        <v>3</v>
+      </c>
+      <c r="T111" t="n">
+        <v>3</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0.2446</v>
+      </c>
+      <c r="W111" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="X111" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>1008.87</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>BTCUSD</t>
+        </is>
+      </c>
+      <c r="AD111" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>36.19</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>supertrend_v7d_half_equity</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>6</v>
+      </c>
+      <c r="D112" t="n">
+        <v>3</v>
+      </c>
+      <c r="E112" t="n">
+        <v>3</v>
+      </c>
+      <c r="F112" t="n">
+        <v>50</v>
+      </c>
+      <c r="G112" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="H112" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I112" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="J112" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="K112" t="n">
+        <v>9.047599999999999</v>
+      </c>
+      <c r="L112" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="M112" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="N112" t="n">
+        <v>3.1449</v>
+      </c>
+      <c r="O112" t="n">
+        <v>7.0713</v>
+      </c>
+      <c r="P112" t="n">
+        <v>-0.7816</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>9.047599999999999</v>
+      </c>
+      <c r="R112" t="n">
+        <v>3.1449</v>
+      </c>
+      <c r="S112" t="n">
+        <v>2</v>
+      </c>
+      <c r="T112" t="n">
+        <v>3</v>
+      </c>
+      <c r="U112" t="n">
+        <v>1.0172</v>
+      </c>
+      <c r="V112" t="n">
+        <v>5.1793</v>
+      </c>
+      <c r="W112" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="X112" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>1018.87</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>BTCUSD</t>
+        </is>
+      </c>
+      <c r="AD112" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>67.37</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>supertrend_v7d_half_equity</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>17</v>
+      </c>
+      <c r="D113" t="n">
+        <v>9</v>
+      </c>
+      <c r="E113" t="n">
+        <v>8</v>
+      </c>
+      <c r="F113" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-5.47</v>
+      </c>
+      <c r="H113" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="I113" t="n">
+        <v>50.47</v>
+      </c>
+      <c r="J113" t="n">
+        <v>-55.94</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0.9022</v>
+      </c>
+      <c r="L113" t="n">
+        <v>-29.53</v>
+      </c>
+      <c r="M113" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="N113" t="n">
+        <v>-0.3219</v>
+      </c>
+      <c r="O113" t="n">
+        <v>5.608</v>
+      </c>
+      <c r="P113" t="n">
+        <v>-6.9931</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0.8018999999999999</v>
+      </c>
+      <c r="R113" t="n">
+        <v>-0.3219</v>
+      </c>
+      <c r="S113" t="n">
+        <v>3</v>
+      </c>
+      <c r="T113" t="n">
+        <v>4</v>
+      </c>
+      <c r="U113" t="n">
+        <v>-0.08989999999999999</v>
+      </c>
+      <c r="V113" t="n">
+        <v>-0.0623</v>
+      </c>
+      <c r="W113" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="X113" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>994.53</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>DOGEUSD</t>
+        </is>
+      </c>
+      <c r="AD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>98.06</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>supertrend_v7d_half_equity</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>15</v>
+      </c>
+      <c r="D114" t="n">
+        <v>8</v>
+      </c>
+      <c r="E114" t="n">
+        <v>7</v>
+      </c>
+      <c r="F114" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="G114" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="H114" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="I114" t="n">
+        <v>42.07</v>
+      </c>
+      <c r="J114" t="n">
+        <v>-43</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="L114" t="n">
+        <v>-29.53</v>
+      </c>
+      <c r="M114" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="N114" t="n">
+        <v>-0.0621</v>
+      </c>
+      <c r="O114" t="n">
+        <v>5.2591</v>
+      </c>
+      <c r="P114" t="n">
+        <v>-6.1435</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="R114" t="n">
+        <v>-0.0621</v>
+      </c>
+      <c r="S114" t="n">
+        <v>3</v>
+      </c>
+      <c r="T114" t="n">
+        <v>4</v>
+      </c>
+      <c r="U114" t="n">
+        <v>-0.0138</v>
+      </c>
+      <c r="V114" t="n">
+        <v>-0.0152</v>
+      </c>
+      <c r="W114" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="X114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>999.0700000000001</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>DOGEUSD</t>
+        </is>
+      </c>
+      <c r="AD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>98.06</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>supertrend_v7d_half_equity</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>2</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" t="n">
+        <v>50</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="H115" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="I115" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="J115" t="n">
+        <v>-12.95</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0.6491</v>
+      </c>
+      <c r="L115" t="n">
+        <v>-20.77</v>
+      </c>
+      <c r="M115" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="N115" t="n">
+        <v>-2.2727</v>
+      </c>
+      <c r="O115" t="n">
+        <v>8.4069</v>
+      </c>
+      <c r="P115" t="n">
+        <v>-12.9522</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0.6491</v>
+      </c>
+      <c r="R115" t="n">
+        <v>-2.2727</v>
+      </c>
+      <c r="S115" t="n">
+        <v>1</v>
+      </c>
+      <c r="T115" t="n">
+        <v>1</v>
+      </c>
+      <c r="U115" t="n">
+        <v>-0.2201</v>
+      </c>
+      <c r="V115" t="n">
+        <v>-0.247</v>
+      </c>
+      <c r="W115" t="n">
+        <v>275</v>
+      </c>
+      <c r="X115" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>995.45</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>DOGEUSD</t>
+        </is>
+      </c>
+      <c r="AD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>33.31</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>supertrend_v7d_half_equity</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>33</v>
+      </c>
+      <c r="D116" t="n">
+        <v>15</v>
+      </c>
+      <c r="E116" t="n">
+        <v>18</v>
+      </c>
+      <c r="F116" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="G116" t="n">
+        <v>-35.17</v>
+      </c>
+      <c r="H116" t="n">
+        <v>-3.52</v>
+      </c>
+      <c r="I116" t="n">
+        <v>35.31</v>
+      </c>
+      <c r="J116" t="n">
+        <v>-70.48</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="L116" t="n">
+        <v>-42.36</v>
+      </c>
+      <c r="M116" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="N116" t="n">
+        <v>-1.0658</v>
+      </c>
+      <c r="O116" t="n">
+        <v>2.3539</v>
+      </c>
+      <c r="P116" t="n">
+        <v>-3.9155</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0.6012</v>
+      </c>
+      <c r="R116" t="n">
+        <v>-1.0658</v>
+      </c>
+      <c r="S116" t="n">
+        <v>3</v>
+      </c>
+      <c r="T116" t="n">
+        <v>4</v>
+      </c>
+      <c r="U116" t="n">
+        <v>-0.8784</v>
+      </c>
+      <c r="V116" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W116" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="X116" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>964.83</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>ETHUSD</t>
+        </is>
+      </c>
+      <c r="AD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>95.34999999999999</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>supertrend_v7d_half_equity</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>25</v>
+      </c>
+      <c r="D117" t="n">
+        <v>10</v>
+      </c>
+      <c r="E117" t="n">
+        <v>15</v>
+      </c>
+      <c r="F117" t="n">
+        <v>40</v>
+      </c>
+      <c r="G117" t="n">
+        <v>-16.62</v>
+      </c>
+      <c r="H117" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="I117" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="J117" t="n">
+        <v>-45.09</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.6314</v>
+      </c>
+      <c r="L117" t="n">
+        <v>-23.8</v>
+      </c>
+      <c r="M117" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="N117" t="n">
+        <v>-0.6649</v>
+      </c>
+      <c r="O117" t="n">
+        <v>2.847</v>
+      </c>
+      <c r="P117" t="n">
+        <v>-3.0062</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="R117" t="n">
+        <v>-0.6649</v>
+      </c>
+      <c r="S117" t="n">
+        <v>3</v>
+      </c>
+      <c r="T117" t="n">
+        <v>4</v>
+      </c>
+      <c r="U117" t="n">
+        <v>-0.6411</v>
+      </c>
+      <c r="V117" t="n">
+        <v>-0.3333</v>
+      </c>
+      <c r="W117" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="X117" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>983.38</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>ETHUSD</t>
+        </is>
+      </c>
+      <c r="AD117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>supertrend_v7d_half_equity</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>8</v>
+      </c>
+      <c r="D118" t="n">
+        <v>5</v>
+      </c>
+      <c r="E118" t="n">
+        <v>3</v>
+      </c>
+      <c r="F118" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-18.86</v>
+      </c>
+      <c r="H118" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="I118" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="J118" t="n">
+        <v>-25.82</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="L118" t="n">
+        <v>-30.71</v>
+      </c>
+      <c r="M118" t="n">
+        <v>-3.05</v>
+      </c>
+      <c r="N118" t="n">
+        <v>-2.3578</v>
+      </c>
+      <c r="O118" t="n">
+        <v>1.3909</v>
+      </c>
+      <c r="P118" t="n">
+        <v>-8.605499999999999</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.1616</v>
+      </c>
+      <c r="R118" t="n">
+        <v>-2.3578</v>
+      </c>
+      <c r="S118" t="n">
+        <v>3</v>
+      </c>
+      <c r="T118" t="n">
+        <v>3</v>
+      </c>
+      <c r="U118" t="n">
+        <v>-1.3046</v>
+      </c>
+      <c r="V118" t="n">
+        <v>-0.6866</v>
+      </c>
+      <c r="W118" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="X118" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>981.14</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>ETHUSD</t>
+        </is>
+      </c>
+      <c r="AD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>97.81</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>out_of_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>supertrend_v7d_half_equity</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>19</v>
+      </c>
+      <c r="D119" t="n">
+        <v>12</v>
+      </c>
+      <c r="E119" t="n">
+        <v>7</v>
+      </c>
+      <c r="F119" t="n">
+        <v>63.16</v>
+      </c>
+      <c r="G119" t="n">
+        <v>59.66</v>
+      </c>
+      <c r="H119" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="I119" t="n">
+        <v>120.38</v>
+      </c>
+      <c r="J119" t="n">
+        <v>-60.71</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1.9827</v>
+      </c>
+      <c r="L119" t="n">
+        <v>-31.83</v>
+      </c>
+      <c r="M119" t="n">
+        <v>-3.13</v>
+      </c>
+      <c r="N119" t="n">
+        <v>3.1402</v>
+      </c>
+      <c r="O119" t="n">
+        <v>10.0316</v>
+      </c>
+      <c r="P119" t="n">
+        <v>-8.673500000000001</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>1.1566</v>
+      </c>
+      <c r="R119" t="n">
+        <v>3.1402</v>
+      </c>
+      <c r="S119" t="n">
+        <v>7</v>
+      </c>
+      <c r="T119" t="n">
+        <v>3</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="W119" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="X119" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>1059.66</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>SOLUSD</t>
+        </is>
+      </c>
+      <c r="AD119" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>97.65000000000001</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>supertrend_v7d_half_equity</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>17</v>
+      </c>
+      <c r="D120" t="n">
+        <v>11</v>
+      </c>
+      <c r="E120" t="n">
+        <v>6</v>
+      </c>
+      <c r="F120" t="n">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="G120" t="n">
+        <v>70.14</v>
+      </c>
+      <c r="H120" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="I120" t="n">
+        <v>115.66</v>
+      </c>
+      <c r="J120" t="n">
+        <v>-45.52</v>
+      </c>
+      <c r="K120" t="n">
+        <v>2.541</v>
+      </c>
+      <c r="L120" t="n">
+        <v>-31.83</v>
+      </c>
+      <c r="M120" t="n">
+        <v>-3.13</v>
+      </c>
+      <c r="N120" t="n">
+        <v>4.1259</v>
+      </c>
+      <c r="O120" t="n">
+        <v>10.5143</v>
+      </c>
+      <c r="P120" t="n">
+        <v>-7.5862</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>1.386</v>
+      </c>
+      <c r="R120" t="n">
+        <v>4.1259</v>
+      </c>
+      <c r="S120" t="n">
+        <v>7</v>
+      </c>
+      <c r="T120" t="n">
+        <v>3</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="V120" t="n">
+        <v>1.0666</v>
+      </c>
+      <c r="W120" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="X120" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>1070.14</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>766.4</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>SOLUSD</t>
+        </is>
+      </c>
+      <c r="AD120" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>97.65000000000001</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>45.51</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>in_sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>supertrend_v7d_half_equity</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>2</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" t="n">
+        <v>50</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-9.789999999999999</v>
+      </c>
+      <c r="H121" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="I121" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="J121" t="n">
+        <v>-14.2</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="L121" t="n">
+        <v>-15.89</v>
+      </c>
+      <c r="M121" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="N121" t="n">
+        <v>-4.8946</v>
+      </c>
+      <c r="O121" t="n">
+        <v>4.4116</v>
+      </c>
+      <c r="P121" t="n">
+        <v>-14.2008</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="R121" t="n">
+        <v>-4.8946</v>
+      </c>
+      <c r="S121" t="n">
+        <v>1</v>
+      </c>
+      <c r="T121" t="n">
+        <v>1</v>
+      </c>
+      <c r="U121" t="n">
+        <v>-0.5526</v>
+      </c>
+      <c r="V121" t="n">
+        <v>-0.6883</v>
+      </c>
+      <c r="W121" t="n">
+        <v>50</v>
+      </c>
+      <c r="X121" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>990.21</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>SOLUSD</t>
+        </is>
+      </c>
+      <c r="AD121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="AH121" t="inlineStr">
         <is>
           <t>out_of_sample</t>
         </is>
@@ -7638,7 +14588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7666,80 +14616,160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>supertrend_v3_strict</t>
+          <t>supertrend_v7d_half_equity</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.975</v>
+        <v>-0.3575</v>
       </c>
       <c r="C2" t="n">
-        <v>-6.7375</v>
+        <v>-1.7675</v>
       </c>
       <c r="D2" t="n">
-        <v>30.2025</v>
+        <v>41.6525</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>supertrend_v5_conservative</t>
+          <t>supertrend_v6b_ultra</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-5.8275</v>
+        <v>-0.7224999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>-8.455</v>
+        <v>-3.51</v>
       </c>
       <c r="D3" t="n">
-        <v>28.8525</v>
+        <v>40.7575</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>supertrend_v4_trend</t>
+          <t>supertrend_v7b_no_stop</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8325</v>
+        <v>-2.555</v>
       </c>
       <c r="C4" t="n">
-        <v>-18.34</v>
+        <v>-5.295</v>
       </c>
       <c r="D4" t="n">
-        <v>28.7925</v>
+        <v>39.545</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>supertrend_v2</t>
+          <t>supertrend_v7c_hard_only</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-36.945</v>
+        <v>-2.555</v>
       </c>
       <c r="C5" t="n">
-        <v>-39.3675</v>
+        <v>-5.295</v>
       </c>
       <c r="D5" t="n">
-        <v>7.385000000000001</v>
+        <v>39.545</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>supertrend_v7a_rsi_entry</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.8025</v>
+      </c>
+      <c r="D6" t="n">
+        <v>38.815</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>supertrend_v3_strict</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-1.975</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-6.7375</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30.2025</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>supertrend_v5_conservative</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-5.8275</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-8.455</v>
+      </c>
+      <c r="D8" t="n">
+        <v>28.8525</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>supertrend_v4_trend</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.8325</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-18.34</v>
+      </c>
+      <c r="D9" t="n">
+        <v>28.7925</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>supertrend_v2</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-36.945</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-39.3675</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7.385000000000001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>supertrend_v1</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B11" t="n">
         <v>-78.1675</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C11" t="n">
         <v>-78.94</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D11" t="n">
         <v>0</v>
       </c>
     </row>
